--- a/consent_forms/030_integrity_pact_agreement_for_structured_cases--consent_forms.xlsx
+++ b/consent_forms/030_integrity_pact_agreement_for_structured_cases--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1142,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_have_checked_and_understand_the_agreement'}</t>
+          <t>yes,_i_have_checked_and_understand_the_agreement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I have checked and understand the agreement'}</t>
+          <t>Yes, I have checked and understand the agreement</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'i,_as_the_authorized_representative_of_,_have_checked_and_signed_this_agreement_on_their_behalf_and_they_have_read_and_signed_this_agreement'}</t>
+          <t>i,_as_the_authorized_representative_of_,_have_checked_and_signed_this_agreement_on_their_behalf_and_they_have_read_and_signed_this_agreement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'I, as the authorized representative of , have checked and signed this agreement on their behalf and they have read and signed this agreement'}</t>
+          <t>I, as the authorized representative of , have checked and signed this agreement on their behalf and they have read and signed this agreement</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'i,_as_the_authorized_representative_of_,_have_checked_and_signed_this_agreement_on_their_behalf_and_they_have_read_and_signed_this_agreement'}</t>
+          <t>i_have_checked_and_signed_this_agreement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'I, as the authorized representative of , have checked and signed this agreement on their behalf and they have read and signed this agreement'}</t>
+          <t>I have checked and signed this agreement</t>
         </is>
       </c>
     </row>
@@ -1328,29 +1328,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_checked_and_signed_this_agreement'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'I have checked and signed this agreement'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>agreement_signatory_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'label':_'none_of_the_above'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
